--- a/AAII_Financials/Yearly/OLED_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OLED_YR_FIN.xlsx
@@ -3125,7 +3125,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>19200</v>
+        <v>19500</v>
       </c>
       <c r="E61" s="3">
         <v>19100</v>
@@ -3176,7 +3176,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>17000</v>
+        <v>16800</v>
       </c>
       <c r="E62" s="3">
         <v>16300</v>
